--- a/artfynd/A 40478-2024 artfynd.xlsx
+++ b/artfynd/A 40478-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121246430</v>
+        <v>121246451</v>
       </c>
       <c r="B2" t="n">
-        <v>105176</v>
+        <v>105186</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,14 +727,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bråtfall ONO 1150 m, Ög</t>
+          <t>Bråtfall O 1240 m, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>538068</v>
+        <v>538164</v>
       </c>
       <c r="R2" t="n">
-        <v>6519408</v>
+        <v>6519261</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121246451</v>
+        <v>121246402</v>
       </c>
       <c r="B3" t="n">
-        <v>105176</v>
+        <v>105186</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -844,21 +844,21 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bråtfall O 1240 m, Ög</t>
+          <t>Bråtfall O 1140 m, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>538164</v>
+        <v>538065</v>
       </c>
       <c r="R3" t="n">
-        <v>6519261</v>
+        <v>6519145</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -923,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121246402</v>
+        <v>121246430</v>
       </c>
       <c r="B4" t="n">
-        <v>105176</v>
+        <v>105186</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -958,7 +958,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -968,21 +968,21 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bråtfall O 1140 m, Ög</t>
+          <t>Bråtfall ONO 1150 m, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>538065</v>
+        <v>538068</v>
       </c>
       <c r="R4" t="n">
-        <v>6519145</v>
+        <v>6519408</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>

--- a/artfynd/A 40478-2024 artfynd.xlsx
+++ b/artfynd/A 40478-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121246451</v>
+        <v>121246430</v>
       </c>
       <c r="B2" t="n">
         <v>105186</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,14 +727,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bråtfall O 1240 m, Ög</t>
+          <t>Bråtfall ONO 1150 m, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>538164</v>
+        <v>538068</v>
       </c>
       <c r="R2" t="n">
-        <v>6519261</v>
+        <v>6519408</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -923,7 +923,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121246430</v>
+        <v>121246451</v>
       </c>
       <c r="B4" t="n">
         <v>105186</v>
@@ -958,7 +958,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -975,14 +975,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bråtfall ONO 1150 m, Ög</t>
+          <t>Bråtfall O 1240 m, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>538068</v>
+        <v>538164</v>
       </c>
       <c r="R4" t="n">
-        <v>6519408</v>
+        <v>6519261</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>

--- a/artfynd/A 40478-2024 artfynd.xlsx
+++ b/artfynd/A 40478-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121246430</v>
       </c>
       <c r="B2" t="n">
-        <v>105186</v>
+        <v>105199</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121246402</v>
+        <v>121246451</v>
       </c>
       <c r="B3" t="n">
-        <v>105186</v>
+        <v>105199</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -844,21 +844,21 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bråtfall O 1140 m, Ög</t>
+          <t>Bråtfall O 1240 m, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>538065</v>
+        <v>538164</v>
       </c>
       <c r="R3" t="n">
-        <v>6519145</v>
+        <v>6519261</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -923,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121246451</v>
+        <v>121246402</v>
       </c>
       <c r="B4" t="n">
-        <v>105186</v>
+        <v>105199</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -958,7 +958,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -968,21 +968,21 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bråtfall O 1240 m, Ög</t>
+          <t>Bråtfall O 1140 m, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>538164</v>
+        <v>538065</v>
       </c>
       <c r="R4" t="n">
-        <v>6519261</v>
+        <v>6519145</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>

--- a/artfynd/A 40478-2024 artfynd.xlsx
+++ b/artfynd/A 40478-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121246430</v>
+        <v>121246402</v>
       </c>
       <c r="B2" t="n">
-        <v>105199</v>
+        <v>105200</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -720,21 +720,21 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bråtfall ONO 1150 m, Ög</t>
+          <t>Bråtfall O 1140 m, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>538068</v>
+        <v>538065</v>
       </c>
       <c r="R2" t="n">
-        <v>6519408</v>
+        <v>6519145</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121246451</v>
+        <v>121246430</v>
       </c>
       <c r="B3" t="n">
-        <v>105199</v>
+        <v>105200</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -851,14 +851,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bråtfall O 1240 m, Ög</t>
+          <t>Bråtfall ONO 1150 m, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>538164</v>
+        <v>538068</v>
       </c>
       <c r="R3" t="n">
-        <v>6519261</v>
+        <v>6519408</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -923,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121246402</v>
+        <v>121246451</v>
       </c>
       <c r="B4" t="n">
-        <v>105199</v>
+        <v>105200</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -958,7 +958,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -968,21 +968,21 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bråtfall O 1140 m, Ög</t>
+          <t>Bråtfall O 1240 m, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>538065</v>
+        <v>538164</v>
       </c>
       <c r="R4" t="n">
-        <v>6519145</v>
+        <v>6519261</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>

--- a/artfynd/A 40478-2024 artfynd.xlsx
+++ b/artfynd/A 40478-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121246402</v>
+        <v>121246430</v>
       </c>
       <c r="B2" t="n">
-        <v>105200</v>
+        <v>105203</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -720,21 +720,21 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bråtfall O 1140 m, Ög</t>
+          <t>Bråtfall ONO 1150 m, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>538065</v>
+        <v>538068</v>
       </c>
       <c r="R2" t="n">
-        <v>6519145</v>
+        <v>6519408</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121246430</v>
+        <v>121246451</v>
       </c>
       <c r="B3" t="n">
-        <v>105200</v>
+        <v>105203</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -851,14 +851,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bråtfall ONO 1150 m, Ög</t>
+          <t>Bråtfall O 1240 m, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>538068</v>
+        <v>538164</v>
       </c>
       <c r="R3" t="n">
-        <v>6519408</v>
+        <v>6519261</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -923,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121246451</v>
+        <v>121246402</v>
       </c>
       <c r="B4" t="n">
-        <v>105200</v>
+        <v>105203</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -958,7 +958,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -968,21 +968,21 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bråtfall O 1240 m, Ög</t>
+          <t>Bråtfall O 1140 m, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>538164</v>
+        <v>538065</v>
       </c>
       <c r="R4" t="n">
-        <v>6519261</v>
+        <v>6519145</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>

--- a/artfynd/A 40478-2024 artfynd.xlsx
+++ b/artfynd/A 40478-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121246430</v>
+        <v>121246402</v>
       </c>
       <c r="B2" t="n">
         <v>105203</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -720,21 +720,21 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bråtfall ONO 1150 m, Ög</t>
+          <t>Bråtfall O 1140 m, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>538068</v>
+        <v>538065</v>
       </c>
       <c r="R2" t="n">
-        <v>6519408</v>
+        <v>6519145</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -923,7 +923,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121246402</v>
+        <v>121246430</v>
       </c>
       <c r="B4" t="n">
         <v>105203</v>
@@ -958,7 +958,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -968,21 +968,21 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bråtfall O 1140 m, Ög</t>
+          <t>Bråtfall ONO 1150 m, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>538065</v>
+        <v>538068</v>
       </c>
       <c r="R4" t="n">
-        <v>6519145</v>
+        <v>6519408</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>

--- a/artfynd/A 40478-2024 artfynd.xlsx
+++ b/artfynd/A 40478-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121246402</v>
+        <v>121246451</v>
       </c>
       <c r="B2" t="n">
-        <v>105203</v>
+        <v>105209</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -720,21 +720,21 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bråtfall O 1140 m, Ög</t>
+          <t>Bråtfall O 1240 m, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>538065</v>
+        <v>538164</v>
       </c>
       <c r="R2" t="n">
-        <v>6519145</v>
+        <v>6519261</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121246451</v>
+        <v>121246430</v>
       </c>
       <c r="B3" t="n">
-        <v>105203</v>
+        <v>105209</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -851,14 +851,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bråtfall O 1240 m, Ög</t>
+          <t>Bråtfall ONO 1150 m, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>538164</v>
+        <v>538068</v>
       </c>
       <c r="R3" t="n">
-        <v>6519261</v>
+        <v>6519408</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -923,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121246430</v>
+        <v>121246402</v>
       </c>
       <c r="B4" t="n">
-        <v>105203</v>
+        <v>105209</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -958,7 +958,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -968,21 +968,21 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bråtfall ONO 1150 m, Ög</t>
+          <t>Bråtfall O 1140 m, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>538068</v>
+        <v>538065</v>
       </c>
       <c r="R4" t="n">
-        <v>6519408</v>
+        <v>6519145</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>

--- a/artfynd/A 40478-2024 artfynd.xlsx
+++ b/artfynd/A 40478-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121246451</v>
+        <v>121246402</v>
       </c>
       <c r="B2" t="n">
-        <v>105209</v>
+        <v>105210</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -720,21 +720,21 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bråtfall O 1240 m, Ög</t>
+          <t>Bråtfall O 1140 m, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>538164</v>
+        <v>538065</v>
       </c>
       <c r="R2" t="n">
-        <v>6519261</v>
+        <v>6519145</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -802,7 +802,7 @@
         <v>121246430</v>
       </c>
       <c r="B3" t="n">
-        <v>105209</v>
+        <v>105210</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -923,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121246402</v>
+        <v>121246451</v>
       </c>
       <c r="B4" t="n">
-        <v>105209</v>
+        <v>105210</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -958,7 +958,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -968,21 +968,21 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bråtfall O 1140 m, Ög</t>
+          <t>Bråtfall O 1240 m, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>538065</v>
+        <v>538164</v>
       </c>
       <c r="R4" t="n">
-        <v>6519145</v>
+        <v>6519261</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>

--- a/artfynd/A 40478-2024 artfynd.xlsx
+++ b/artfynd/A 40478-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121246402</v>
+        <v>121246430</v>
       </c>
       <c r="B2" t="n">
         <v>105210</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -720,21 +720,21 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bråtfall O 1140 m, Ög</t>
+          <t>Bråtfall ONO 1150 m, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>538065</v>
+        <v>538068</v>
       </c>
       <c r="R2" t="n">
-        <v>6519145</v>
+        <v>6519408</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -799,7 +799,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121246430</v>
+        <v>121246451</v>
       </c>
       <c r="B3" t="n">
         <v>105210</v>
@@ -834,7 +834,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -851,14 +851,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bråtfall ONO 1150 m, Ög</t>
+          <t>Bråtfall O 1240 m, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>538068</v>
+        <v>538164</v>
       </c>
       <c r="R3" t="n">
-        <v>6519408</v>
+        <v>6519261</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -923,7 +923,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121246451</v>
+        <v>121246402</v>
       </c>
       <c r="B4" t="n">
         <v>105210</v>
@@ -958,7 +958,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -968,21 +968,21 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bråtfall O 1240 m, Ög</t>
+          <t>Bråtfall O 1140 m, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>538164</v>
+        <v>538065</v>
       </c>
       <c r="R4" t="n">
-        <v>6519261</v>
+        <v>6519145</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>

--- a/artfynd/A 40478-2024 artfynd.xlsx
+++ b/artfynd/A 40478-2024 artfynd.xlsx
@@ -799,7 +799,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121246451</v>
+        <v>121246402</v>
       </c>
       <c r="B3" t="n">
         <v>105210</v>
@@ -834,7 +834,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -844,21 +844,21 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bråtfall O 1240 m, Ög</t>
+          <t>Bråtfall O 1140 m, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>538164</v>
+        <v>538065</v>
       </c>
       <c r="R3" t="n">
-        <v>6519261</v>
+        <v>6519145</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -923,7 +923,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121246402</v>
+        <v>121246451</v>
       </c>
       <c r="B4" t="n">
         <v>105210</v>
@@ -958,7 +958,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -968,21 +968,21 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bråtfall O 1140 m, Ög</t>
+          <t>Bråtfall O 1240 m, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>538065</v>
+        <v>538164</v>
       </c>
       <c r="R4" t="n">
-        <v>6519145</v>
+        <v>6519261</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>

--- a/artfynd/A 40478-2024 artfynd.xlsx
+++ b/artfynd/A 40478-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121246430</v>
+        <v>121246402</v>
       </c>
       <c r="B2" t="n">
         <v>105210</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -720,21 +720,21 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bråtfall ONO 1150 m, Ög</t>
+          <t>Bråtfall O 1140 m, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>538068</v>
+        <v>538065</v>
       </c>
       <c r="R2" t="n">
-        <v>6519408</v>
+        <v>6519145</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -799,7 +799,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121246402</v>
+        <v>121246430</v>
       </c>
       <c r="B3" t="n">
         <v>105210</v>
@@ -834,7 +834,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -844,21 +844,21 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bråtfall O 1140 m, Ög</t>
+          <t>Bråtfall ONO 1150 m, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>538065</v>
+        <v>538068</v>
       </c>
       <c r="R3" t="n">
-        <v>6519145</v>
+        <v>6519408</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
